--- a/templates/inventory_template_0.xlsx
+++ b/templates/inventory_template_0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mickey_wang/Workspace/pdf_invoice_parser/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDBD9A79-6292-1246-84DF-D29C10D60A0F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1666CC5-5861-7646-801F-E4D96F362AAC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8000" yWindow="3900" windowWidth="27840" windowHeight="16940" xr2:uid="{B46F508C-1DBE-8841-ACEE-DE903A2297B3}"/>
   </bookViews>
@@ -194,7 +194,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -236,6 +236,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -572,10 +575,10 @@
       <c r="I1" s="10"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="14"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="14"/>
       <c r="D2" s="14"/>
       <c r="E2" s="14"/>
